--- a/Day3/data4modelportion.xlsx
+++ b/Day3/data4modelportion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doratortarolo/Documents/Didattica/2025-2026_PhD_FromDatatoModels/From-Data-to-Models/Day3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A8E8DD-C194-DF4C-8AC3-D41D160CD73A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8C02BB-C3E7-3443-8385-5B16CADA66F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9380" yWindow="1100" windowWidth="27240" windowHeight="16060" activeTab="2" xr2:uid="{9DD5C123-5A0D-BD41-A9E1-0497CBDEA970}"/>
   </bookViews>
